--- a/RF Remote Control Requirements .xlsx
+++ b/RF Remote Control Requirements .xlsx
@@ -5,23 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TuongMinh\University\Semester 252\Embedded System Design\BTL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A192806-B4B5-43D1-B2D4-67CACB7CCD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6ED83DC-621A-4A0E-A91E-3B72C9E18241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements " sheetId="1" r:id="rId1"/>
-    <sheet name="Components" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Components" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -187,21 +188,6 @@
     <t>Receiver shall provide 4 active-high logic outputs compatible with 5V levels.</t>
   </si>
   <si>
-    <t xml:space="preserve">RF MODULE </t>
-  </si>
-  <si>
-    <t>Module RF 2.4GHz Si24R1 NF-01-S Ai-Thinker</t>
-  </si>
-  <si>
-    <t>Antenna</t>
-  </si>
-  <si>
-    <t>Anten 433Mhz 3dbi Ipex</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RF module with antenna</t>
-  </si>
-  <si>
     <t>Module RF 2.4GHz NRF24L01 + PA + LNA anten rời</t>
   </si>
   <si>
@@ -382,12 +368,318 @@
       <t xml:space="preserve"> All unused GPIO pins on the Microcontroller shall be configured either as Outputs driven LOW, or as Inputs with Internal Pull-Up resistors enabled.</t>
     </r>
   </si>
+  <si>
+    <t>RF module with antenna</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Look for the method of transmitting and receiving using the module via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DATASHEET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Transmitter shall send control commands wirelessly using the nRF24L01+ module at 2.4 GHz.</t>
+  </si>
+  <si>
+    <r>
+      <t>R.F-1.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t xml:space="preserve"> Module shall give a "Preamble" Sequence </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t xml:space="preserve">R.F-1.3: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>The unique 8-bit ID shall be stored in the AVR microcontroller's EEPROM memory to ensure retention during power loss</t>
+    </r>
+  </si>
+  <si>
+    <t>Button-based command input</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>R.F-2.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>: Transmitter shall support at least 4 push buttons</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.F-2.2: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>Each button shall execute an unique command</t>
+    </r>
+  </si>
+  <si>
+    <t>R.F-5</t>
+  </si>
+  <si>
+    <t>Address Filtering</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.F-5.1: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>The receiver shall only respond to packets with the correct address and device ID.</t>
+    </r>
+  </si>
+  <si>
+    <t>Status Indication</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.F-4.1: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t xml:space="preserve">Microcontroller shall control the status LED via one GPIO: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="7"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>GREEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t xml:space="preserve"> for successful transmission and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="6"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>YELLOW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t xml:space="preserve"> for on-going event.</t>
+    </r>
+  </si>
+  <si>
+    <t>R.P-1 
+(Performance requirement)</t>
+  </si>
+  <si>
+    <t>RF Transmitter shall transmit the control signal at a distance of 10 meter indoor</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.F-5.2: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>The system shall use 5-byte RF address and 1 communication pipe.</t>
+    </r>
+  </si>
+  <si>
+    <t>System shall operate on a carrier frequency of 2400 MHz ± 76 kHz.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t xml:space="preserve">R.F-3.1: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>The system shall operate at 250 kbps or 1000 kbps for short range</t>
+    </r>
+  </si>
+  <si>
+    <t>R.P-4</t>
+  </si>
+  <si>
+    <t>Response Time</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.P-4.1: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>The receiver shall respond within 100ms after the button press</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.P-4.2: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>The system shall be operational within 1s after power-up</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.P-1.3: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>Transmitter shall include voltage regulator if using 5V AVR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.P-1.4: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>Receiver shall include a stable supply at 3.3V using proper decoupling capacitor</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.P-1.1: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>Transmitter shall utilize a quarter-wave monopole antenna (wire or PCB trace) with a length of approximately 17.3 cm.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>R.I-1 
+(Interface requirement)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R.F-2.3: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Lora"/>
+      </rPr>
+      <t>Button shall be debounced in software</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -425,12 +717,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Lora"/>
@@ -438,6 +724,51 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Lora"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Lora"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="7"/>
+      <name val="Lora"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="6"/>
       <name val="Lora"/>
     </font>
   </fonts>
@@ -461,7 +792,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -469,11 +800,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -496,27 +845,97 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -735,12 +1154,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G1009"/>
+  <dimension ref="A1:G1015"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="46.77734375" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" customWidth="1"/>
+    <col min="3" max="3" width="73.44140625" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
   </cols>
@@ -761,282 +1180,330 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>6</v>
+      <c r="B2" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="5" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="D5" s="5"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="A6" s="33"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="11"/>
       <c r="C7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>16</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D7" s="5"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:7" ht="52.2" x14ac:dyDescent="0.45">
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="1:7" ht="69" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>20</v>
+      <c r="B9" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:7" ht="69.599999999999994" x14ac:dyDescent="0.45">
-      <c r="A12" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:7" ht="69.599999999999994" x14ac:dyDescent="0.45">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>25</v>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" s="29" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="25"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+    </row>
+    <row r="13" spans="1:7" s="29" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+    </row>
+    <row r="14" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+    </row>
+    <row r="15" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="34"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:7" ht="79.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="34"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="4" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" spans="1:7" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="11"/>
-      <c r="B17" s="13"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+    </row>
+    <row r="17" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="34"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="4" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="12" t="s">
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:7" ht="79.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="1:7" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="9"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="1:7" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="1:7" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="26"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" spans="1:7" ht="63" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="3" t="s">
+      <c r="C24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" spans="1:7" ht="63" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-    </row>
-    <row r="21" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
-      <c r="C23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B27" s="6"/>
@@ -4970,21 +5437,49 @@
       <c r="B1009" s="6"/>
       <c r="C1009" s="7"/>
     </row>
+    <row r="1010" spans="2:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B1010" s="6"/>
+      <c r="C1010" s="7"/>
+    </row>
+    <row r="1011" spans="2:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B1011" s="6"/>
+      <c r="C1011" s="7"/>
+    </row>
+    <row r="1012" spans="2:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B1012" s="6"/>
+      <c r="C1012" s="7"/>
+    </row>
+    <row r="1013" spans="2:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B1013" s="6"/>
+      <c r="C1013" s="7"/>
+    </row>
+    <row r="1014" spans="2:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B1014" s="6"/>
+      <c r="C1014" s="7"/>
+    </row>
+    <row r="1015" spans="2:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B1015" s="6"/>
+      <c r="C1015" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="19">
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="F2:G3"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="A5:A7"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="F2:G3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
   </mergeCells>
@@ -4994,46 +5489,348 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A0484C3-F406-4534-AB68-893C51BB95C4}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="52.77734375" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="52.2" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" spans="1:7" ht="303" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" ht="243.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:7" ht="330.6" x14ac:dyDescent="0.45">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+    </row>
+    <row r="5" spans="1:7" ht="330.6" x14ac:dyDescent="0.45">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="1:7" ht="400.2" x14ac:dyDescent="0.45">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" spans="1:7" ht="330.6" x14ac:dyDescent="0.45">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="1:7" ht="174" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+    </row>
+    <row r="9" spans="1:7" ht="174" x14ac:dyDescent="0.45">
+      <c r="A9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" ht="226.2" x14ac:dyDescent="0.45">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" ht="313.2" x14ac:dyDescent="0.45">
+      <c r="A12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" spans="1:7" ht="400.2" x14ac:dyDescent="0.45">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" spans="1:7" ht="208.8" x14ac:dyDescent="0.45">
+      <c r="A14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+    </row>
+    <row r="15" spans="1:7" ht="365.4" x14ac:dyDescent="0.45">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" spans="1:7" ht="382.8" x14ac:dyDescent="0.45">
+      <c r="A16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+    </row>
+    <row r="17" spans="1:7" ht="226.2" x14ac:dyDescent="0.45">
+      <c r="A17" s="9"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:7" ht="330.6" x14ac:dyDescent="0.45">
+      <c r="A18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" spans="1:7" ht="330.6" x14ac:dyDescent="0.45">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:7" ht="191.4" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="F2:G3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:3" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
+      <c r="C1" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+    </row>
+    <row r="3" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="B1" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>